--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120096987</v>
+        <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>78730</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413934</v>
+        <v>413878</v>
       </c>
       <c r="R2" t="n">
-        <v>6966040</v>
+        <v>6966236</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096987</t>
+          <t>https://artportalen.se/Sighting/136828001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064777</v>
+        <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>80461</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnen, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413940</v>
+        <v>413885</v>
       </c>
       <c r="R3" t="n">
-        <v>6966074</v>
+        <v>6966214</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,16 +867,1046 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828003</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136828006</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6966051</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828006</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136828008</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>413935</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6966044</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828008</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136828005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>413927</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966138</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828005</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136828007</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>413935</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966044</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828007</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136828000</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92076</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>413865</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966228</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120096987</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966040</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096987</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136827958</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>413959</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966116</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827958</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136828004</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>413895</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6966181</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828004</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136828002</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>413885</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6966228</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120064777</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>413940</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6966074</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120064777</t>
         </is>
@@ -896,6 +1916,16 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828006</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828008</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136827958</v>
       </c>
       <c r="B10" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136828004</v>
       </c>
       <c r="B11" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136828002</v>
       </c>
       <c r="B12" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828006</v>
       </c>
       <c r="B4" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828008</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136827958</v>
       </c>
       <c r="B10" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136828004</v>
       </c>
       <c r="B11" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136828002</v>
       </c>
       <c r="B12" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828006</v>
       </c>
       <c r="B4" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828008</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136827958</v>
       </c>
       <c r="B10" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136828004</v>
       </c>
       <c r="B11" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136828002</v>
       </c>
       <c r="B12" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120096987</v>
+        <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>78730</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413934</v>
+        <v>413878</v>
       </c>
       <c r="R2" t="n">
-        <v>6966040</v>
+        <v>6966236</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096987</t>
+          <t>https://artportalen.se/Sighting/136828001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064777</v>
+        <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>80461</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnen, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413940</v>
+        <v>413885</v>
       </c>
       <c r="R3" t="n">
-        <v>6966074</v>
+        <v>6966214</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,16 +867,1046 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828003</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136828006</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79151</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6966051</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828006</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136828008</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79151</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>413935</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6966044</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828008</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136828005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92307</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>413927</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966138</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828005</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136828007</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92050</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>413935</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966044</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828007</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136828000</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92091</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>413865</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966228</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120096987</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966040</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096987</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136827958</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79242</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>413959</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966116</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827958</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136828004</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79242</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>413895</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6966181</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828004</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136828002</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80104</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>413885</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6966228</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120064777</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>413940</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6966074</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120064777</t>
         </is>
@@ -896,6 +1916,16 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120096987</v>
+        <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>78730</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413934</v>
+        <v>413878</v>
       </c>
       <c r="R2" t="n">
-        <v>6966040</v>
+        <v>6966236</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096987</t>
+          <t>https://artportalen.se/Sighting/136828001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120064777</v>
+        <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>80461</v>
+        <v>79154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnen, Hjd</t>
+          <t>Långtjärnberget, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413940</v>
+        <v>413885</v>
       </c>
       <c r="R3" t="n">
-        <v>6966074</v>
+        <v>6966214</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,16 +867,1046 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828003</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136828006</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79154</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6966051</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828006</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136828008</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79154</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>413935</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6966044</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828008</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136828005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92309</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>413927</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966138</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828005</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136828007</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92052</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>413935</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966044</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828007</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136828000</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92093</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>413865</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966228</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120096987</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966040</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096987</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136827958</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79245</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>413959</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966116</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827958</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136828004</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79245</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>413895</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6966181</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828004</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136828002</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80107</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>413885</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6966228</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120064777</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>413940</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6966074</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120064777</t>
         </is>
@@ -896,6 +1916,16 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828006</v>
       </c>
       <c r="B4" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828008</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92052</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136827958</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136828004</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136828002</v>
       </c>
       <c r="B12" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828006</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828008</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136827958</v>
       </c>
       <c r="B10" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136828004</v>
       </c>
       <c r="B11" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136828002</v>
       </c>
       <c r="B12" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828006</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828008</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92070</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136827958</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136828004</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136828002</v>
       </c>
       <c r="B12" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828006</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828008</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136827958</v>
       </c>
       <c r="B10" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136828004</v>
       </c>
       <c r="B11" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136828002</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92084</v>
+        <v>92086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828006</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828008</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92086</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136827958</v>
       </c>
       <c r="B10" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136828004</v>
       </c>
       <c r="B11" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136828002</v>
       </c>
       <c r="B12" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 47858-2025 artfynd.xlsx
+++ b/artfynd/A 47858-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828001</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136828003</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136828006</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136828008</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136828005</v>
       </c>
       <c r="B6" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136828007</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136828000</v>
       </c>
       <c r="B8" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>136827958</v>
       </c>
       <c r="B10" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>136828004</v>
       </c>
       <c r="B11" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>136828002</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
